--- a/docs/StructureDefinition-LTCServiceRequest.xlsx
+++ b/docs/StructureDefinition-LTCServiceRequest.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="534">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -953,6 +953,168 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding:ltcServiceItem</t>
+  </si>
+  <si>
+    <t>ltcServiceItem</t>
+  </si>
+  <si>
+    <t>臺灣長照服務項目代碼（AA..GA 系列）</t>
+  </si>
+  <si>
+    <t>http://ltc-ig.fhir.tw/ValueSet/vs-tw-ltc-service-item</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding:ltcServiceItem.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding.id</t>
+  </si>
+  <si>
+    <t>resource中資料項目的唯一ID（用於內部參照），這可以是任何不含空格的字串。</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding:ltcServiceItem.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding.extension</t>
+  </si>
+  <si>
+    <t>可用於表示不屬於此資料項目基本定義的附加資訊。為了擴充的使用安全和可管理，對擴充的定義和使用有一套嚴格的管理。儘管任何實作者都可以定義一個擴充，但作為擴充定義的一部分，有一套要求 **必須（SHALL）** 滿足。</t>
+  </si>
+  <si>
+    <t>無論使用或定義擴充的機構或管轄區，任何應用程式、專案或標準使用擴充都不背負任何污名（stigma）。使用擴充是允許FHIR規範為每個人保留一個核心的簡易性。</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding:ltcServiceItem.system</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding.system</t>
+  </si>
+  <si>
+    <t>專門術語系統（terminology system）的識別</t>
+  </si>
+  <si>
+    <t>定義代碼中符號意義的代碼系統識別</t>
+  </si>
+  <si>
+    <t>URI可以是一個OID（urn:oid:...）或一個UUID（urn:uuid:...）；OID和UUID **必須（SHALL）** 參照HL7 OID註冊中心；否則，URI應該來自HL7的FHIR定義的特殊URI列表，或者它應該參照一些明確建立的系统定義。</t>
+  </si>
+  <si>
+    <t>需要明確說明符號定義的來源</t>
+  </si>
+  <si>
+    <t>http://ltc-ig.fhir.tw/CodeSystem/cs-tw-ltc-service-item</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding:ltcServiceItem.version</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding.version</t>
+  </si>
+  <si>
+    <t>系統的版本—如果相關的話</t>
+  </si>
+  <si>
+    <t>選擇此代碼時使用的代碼系統版本；請注意，一個維護良好的代碼系統不需要版本報告，因為代碼的意義在不同系統版本中是一致的；然而，不能始終保證這點，當不能保證意義一致時， **必須（SHALL）** 將版本資訊也一併作交換。</t>
+  </si>
+  <si>
+    <t>如果專門術語沒有明確定義應該使用什麼字串來識別代碼系統的版本，建議使用版本正式發布的日期（用FHIR日期格式表示）作為版本日期。</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding:ltcServiceItem.code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding.code</t>
+  </si>
+  <si>
+    <t>系統定義的語法之符號</t>
+  </si>
+  <si>
+    <t>系統定義的語法之符號；符號可能是一個預先定義的代碼，也可能是代碼系統定義的語法中的表達式（如後組合配對／後組合式）。</t>
+  </si>
+  <si>
+    <t>需要參照系統中的一個特定代碼</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding:ltcServiceItem.display</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding.display</t>
+  </si>
+  <si>
+    <t>由系統定義的表示法</t>
+  </si>
+  <si>
+    <t>遵循系統的規則以呈現代碼含義的表示法</t>
+  </si>
+  <si>
+    <t>需要能為不了解此系統的讀者呈現可讀的代碼含義</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding:ltcServiceItem.userSelected</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>此編碼是否由使用者直接選擇？</t>
+  </si>
+  <si>
+    <t>表明此編碼是由使用者直接選擇，例如：從可用項目（代碼或顯示名稱）的清單中選擇。</t>
+  </si>
+  <si>
+    <t>在一系列備選方案中，直接選擇的代碼是新翻譯最合適的起點；關於「直接選擇」的確切意義，存在模糊不清之處，可能需要貿易夥伴的同意，以更完整澄清此資料項目的使用及其後果。</t>
+  </si>
+  <si>
+    <t>已被確定為一個臨床安全準則—此確切的系統／代碼對(code pair)是被明確選擇的，而不是由系統根據一些規則或是程式語言處理判斷。</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>ServiceRequest.code.text</t>
@@ -1829,11 +1991,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO54"/>
+  <dimension ref="A1:AO62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.6953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.62109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.77734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.9453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -5643,9 +5805,11 @@
         <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5666,19 +5830,19 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5703,13 +5867,11 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5727,13 +5889,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5745,10 +5907,10 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5759,21 +5921,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5782,20 +5944,18 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5820,13 +5980,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>316</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5844,42 +6004,42 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>318</v>
+        <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5890,7 +6050,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5899,21 +6059,21 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>320</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5949,40 +6109,40 @@
         <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>275</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>318</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -5993,10 +6153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6019,16 +6179,20 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>326</v>
+        <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6037,7 +6201,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -6076,10 +6240,10 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -6091,31 +6255,31 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>329</v>
+        <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6125,7 +6289,7 @@
         <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -6134,15 +6298,17 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>336</v>
+        <v>266</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6191,7 +6357,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6206,35 +6372,35 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
@@ -6249,16 +6415,18 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6306,7 +6474,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6321,27 +6489,27 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6355,7 +6523,7 @@
         <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -6364,16 +6532,18 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>266</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6397,13 +6567,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6421,7 +6591,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6439,28 +6609,28 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>20</v>
+        <v>345</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6470,7 +6640,7 @@
         <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -6479,16 +6649,20 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>364</v>
+        <v>245</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6536,7 +6710,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6551,31 +6725,31 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>367</v>
+        <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6594,18 +6768,20 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>374</v>
+        <v>266</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6653,7 +6829,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6668,38 +6844,38 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6714,13 +6890,13 @@
         <v>230</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6749,10 +6925,10 @@
         <v>221</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6770,56 +6946,56 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>392</v>
+        <v>262</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>395</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
@@ -6831,15 +7007,15 @@
         <v>374</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6887,13 +7063,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -6902,27 +7078,27 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>399</v>
+        <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6930,13 +7106,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -6945,13 +7121,13 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6978,13 +7154,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>405</v>
+        <v>20</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7002,13 +7178,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -7017,41 +7193,41 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>20</v>
+        <v>384</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>20</v>
+        <v>389</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -7060,13 +7236,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7117,13 +7293,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -7132,38 +7308,38 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>20</v>
+        <v>394</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>20</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>90</v>
@@ -7175,17 +7351,15 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7210,11 +7384,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7232,13 +7408,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -7247,27 +7423,27 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7278,10 +7454,10 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
@@ -7290,17 +7466,15 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7325,13 +7499,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>20</v>
+        <v>412</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7349,13 +7523,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -7364,56 +7538,56 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>428</v>
+        <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>20</v>
+        <v>417</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7464,13 +7638,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -7479,59 +7653,59 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7581,13 +7755,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7596,38 +7770,38 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>20</v>
+        <v>435</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>20</v>
+        <v>436</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>438</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7639,16 +7813,16 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>447</v>
+        <v>230</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7674,13 +7848,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>20</v>
+        <v>442</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>20</v>
+        <v>443</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7698,13 +7872,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -7713,31 +7887,31 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>20</v>
+        <v>444</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7747,7 +7921,7 @@
         <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>20</v>
@@ -7756,20 +7930,18 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>428</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -7793,13 +7965,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>459</v>
+        <v>20</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7817,7 +7989,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7832,27 +8004,27 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>462</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7866,22 +8038,22 @@
         <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>464</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>50</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7908,13 +8080,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>20</v>
+        <v>459</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>20</v>
+        <v>460</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7932,7 +8104,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7947,27 +8119,27 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>466</v>
+        <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>318</v>
+        <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>468</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7978,7 +8150,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7990,13 +8162,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>266</v>
+        <v>463</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8047,13 +8219,13 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
@@ -8065,24 +8237,24 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>318</v>
+        <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8096,25 +8268,25 @@
         <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>474</v>
+        <v>230</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8140,13 +8312,11 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>20</v>
+        <v>471</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8164,7 +8334,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8179,23 +8349,955 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AM54" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AM62" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO54">
+  <autoFilter ref="A1:AO62">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8205,7 +9307,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LTCServiceRequest.xlsx
+++ b/docs/StructureDefinition-LTCServiceRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
